--- a/astro-site/public/dl/kit-tareas/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas/03-tareas-manager.xlsx
@@ -1,23 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Diario Manager" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Semanal Manager" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mensual Manager" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Handover Turno" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diario Manager" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semanal Manager" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual Manager" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Handover Turno" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Diario Manager'!$A$1:$G$44</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Semanal Manager'!$A$1:$G$41</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Mensual Manager'!$A$1:$G$36</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'Handover Turno'!$A$1:$G$28</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Diario Manager'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Diario Manager'!$A$1:$G$44</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Semanal Manager'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Semanal Manager'!$A$1:$G$41</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mensual Manager'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Mensual Manager'!$A$1:$G$36</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Handover Turno'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Handover Turno'!$A$1:$G$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -137,7 +141,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -159,59 +163,118 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="28">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -571,15 +634,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B11"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -587,6 +651,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -594,9 +659,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -625,9 +688,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" t="inlineStr"/>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
@@ -635,8 +696,33 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -645,18 +731,18 @@
   <sheetPr>
     <tabColor rgb="00FF9800"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -673,10 +759,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -701,7 +788,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -716,18 +803,16 @@
           <t xml:space="preserve">  PRIMERA HORA (llegada)</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -753,10 +838,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="27" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -782,10 +865,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="27" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -811,10 +892,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="27" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -840,10 +919,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -868,24 +945,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  PRE-SERVICIO</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="B12" s="25" t="n"/>
+      <c r="C12" s="25" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="25" t="n"/>
+      <c r="F12" s="25" t="n"/>
+      <c r="G12" s="26" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="27" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -911,10 +987,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="27" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -940,10 +1014,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="27" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -969,10 +1041,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="27" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -998,10 +1068,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="27" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1026,24 +1094,23 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="15" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  DURANTE SERVICIO</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
-      <c r="F19" s="17" t="n"/>
-      <c r="G19" s="17" t="n"/>
+      <c r="B19" s="25" t="n"/>
+      <c r="C19" s="25" t="n"/>
+      <c r="D19" s="25" t="n"/>
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="25" t="n"/>
+      <c r="G19" s="26" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="27" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1069,10 +1136,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="27" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1098,10 +1163,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="27" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -1127,10 +1190,8 @@
       <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="27" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -1155,24 +1216,23 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="15" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  POST-SERVICIO</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
+      <c r="B25" s="25" t="n"/>
+      <c r="C25" s="25" t="n"/>
+      <c r="D25" s="25" t="n"/>
+      <c r="E25" s="25" t="n"/>
+      <c r="F25" s="25" t="n"/>
+      <c r="G25" s="26" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="27" t="n">
+        <v>15</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -1198,10 +1258,8 @@
       <c r="G26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="27" t="n">
+        <v>16</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
@@ -1227,10 +1285,8 @@
       <c r="G27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="27" t="n">
+        <v>17</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
@@ -1256,10 +1312,8 @@
       <c r="G28" s="15" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A29" s="27" t="n">
+        <v>18</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -1285,10 +1339,8 @@
       <c r="G29" s="15" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A30" s="27" t="n">
+        <v>19</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
@@ -1313,24 +1365,23 @@
       <c r="F30" s="14" t="n"/>
       <c r="G30" s="15" t="n"/>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  CIERRE DEL DÍA</t>
         </is>
       </c>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="8" t="n"/>
+      <c r="B32" s="25" t="n"/>
+      <c r="C32" s="25" t="n"/>
+      <c r="D32" s="25" t="n"/>
+      <c r="E32" s="25" t="n"/>
+      <c r="F32" s="25" t="n"/>
+      <c r="G32" s="26" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A33" s="27" t="n">
+        <v>20</v>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
@@ -1356,10 +1407,8 @@
       <c r="G33" s="15" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A34" s="27" t="n">
+        <v>21</v>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
@@ -1385,10 +1434,8 @@
       <c r="G34" s="15" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A35" s="27" t="n">
+        <v>22</v>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
@@ -1414,10 +1461,8 @@
       <c r="G35" s="15" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A36" s="27" t="n">
+        <v>23</v>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
@@ -1443,10 +1488,8 @@
       <c r="G36" s="15" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A37" s="27" t="n">
+        <v>24</v>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
@@ -1471,6 +1514,8 @@
       <c r="F37" s="14" t="n"/>
       <c r="G37" s="15" t="n"/>
     </row>
+    <row r="38"/>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
         <is>
@@ -1479,17 +1524,19 @@
       </c>
       <c r="D40" s="19">
         <f>COUNTIF(F5:F38,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F40" s="19" t="n">
-        <v>24</v>
-      </c>
-    </row>
+      <c r="F40" s="19">
+        <f>COUNTIF(B5:B38,"?*")</f>
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="19" t="inlineStr">
         <is>
@@ -1497,13 +1544,17 @@
         </is>
       </c>
       <c r="B42" s="15" t="n"/>
+      <c r="C42" s="25" t="n"/>
+      <c r="D42" s="26" t="n"/>
       <c r="E42" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F42" s="15" t="n"/>
-    </row>
+      <c r="G42" s="26" t="n"/>
+    </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="21" t="inlineStr">
         <is>
@@ -1524,13 +1575,26 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="F42:G42"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G38">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30 F33 F34 F35 F36 F37" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30 F33 F34 F35 F36 F37 F38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1539,18 +1603,18 @@
   <sheetPr>
     <tabColor rgb="00E65100"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1567,10 +1631,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1595,7 +1660,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1610,18 +1675,16 @@
           <t xml:space="preserve">  LUNES — PLANIFICACIÓN</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1647,10 +1710,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="27" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1676,10 +1737,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="27" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1705,10 +1764,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="27" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1734,10 +1791,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -1762,24 +1817,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  MARTES — PROVEEDORES</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="B12" s="25" t="n"/>
+      <c r="C12" s="25" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="25" t="n"/>
+      <c r="F12" s="25" t="n"/>
+      <c r="G12" s="26" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="27" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -1805,10 +1859,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="27" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -1834,10 +1886,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="27" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -1863,10 +1913,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="27" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -1891,24 +1939,23 @@
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="15" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  MIÉRCOLES — EQUIPO</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
+      <c r="B18" s="25" t="n"/>
+      <c r="C18" s="25" t="n"/>
+      <c r="D18" s="25" t="n"/>
+      <c r="E18" s="25" t="n"/>
+      <c r="F18" s="25" t="n"/>
+      <c r="G18" s="26" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="27" t="n">
+        <v>10</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -1934,10 +1981,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="27" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1963,10 +2008,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="27" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1992,10 +2035,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="27" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -2020,24 +2061,23 @@
       <c r="F22" s="14" t="n"/>
       <c r="G22" s="15" t="n"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  JUEVES — CALIDAD</t>
         </is>
       </c>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
+      <c r="B24" s="25" t="n"/>
+      <c r="C24" s="25" t="n"/>
+      <c r="D24" s="25" t="n"/>
+      <c r="E24" s="25" t="n"/>
+      <c r="F24" s="25" t="n"/>
+      <c r="G24" s="26" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="27" t="n">
+        <v>14</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -2063,10 +2103,8 @@
       <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="27" t="n">
+        <v>15</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -2092,10 +2130,8 @@
       <c r="G26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="27" t="n">
+        <v>16</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
@@ -2121,10 +2157,8 @@
       <c r="G27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="27" t="n">
+        <v>17</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
@@ -2149,24 +2183,23 @@
       <c r="F28" s="14" t="n"/>
       <c r="G28" s="15" t="n"/>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  VIERNES — MARKETING Y ADMIN</t>
         </is>
       </c>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="8" t="n"/>
+      <c r="B30" s="25" t="n"/>
+      <c r="C30" s="25" t="n"/>
+      <c r="D30" s="25" t="n"/>
+      <c r="E30" s="25" t="n"/>
+      <c r="F30" s="25" t="n"/>
+      <c r="G30" s="26" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A31" s="27" t="n">
+        <v>18</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
@@ -2192,10 +2225,8 @@
       <c r="G31" s="15" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A32" s="27" t="n">
+        <v>19</v>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
@@ -2221,10 +2252,8 @@
       <c r="G32" s="15" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A33" s="27" t="n">
+        <v>20</v>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
@@ -2250,10 +2279,8 @@
       <c r="G33" s="15" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A34" s="27" t="n">
+        <v>21</v>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
@@ -2278,6 +2305,8 @@
       <c r="F34" s="14" t="n"/>
       <c r="G34" s="15" t="n"/>
     </row>
+    <row r="35"/>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
@@ -2286,17 +2315,19 @@
       </c>
       <c r="D37" s="19">
         <f>COUNTIF(F5:F35,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E37" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F37" s="19" t="n">
-        <v>21</v>
-      </c>
-    </row>
+      <c r="F37" s="19">
+        <f>COUNTIF(B5:B35,"?*")</f>
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
         <is>
@@ -2304,13 +2335,17 @@
         </is>
       </c>
       <c r="B39" s="15" t="n"/>
+      <c r="C39" s="25" t="n"/>
+      <c r="D39" s="26" t="n"/>
       <c r="E39" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F39" s="15" t="n"/>
-    </row>
+      <c r="G39" s="26" t="n"/>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
         <is>
@@ -2323,21 +2358,34 @@
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="F39:G39"/>
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B39:D39"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G35">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F19 F20 F21 F22 F25 F26 F27 F28 F31 F32 F33 F34" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F19 F20 F21 F22 F25 F26 F27 F28 F31 F32 F33 F34 F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2346,18 +2394,18 @@
   <sheetPr>
     <tabColor rgb="00BF360C"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2374,10 +2422,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2402,7 +2451,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2417,18 +2466,16 @@
           <t xml:space="preserve">  FINANZAS</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -2454,10 +2501,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="27" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -2483,10 +2528,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="27" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -2512,10 +2555,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="27" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -2541,10 +2582,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -2569,24 +2608,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  EQUIPO</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="B12" s="25" t="n"/>
+      <c r="C12" s="25" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="25" t="n"/>
+      <c r="F12" s="25" t="n"/>
+      <c r="G12" s="26" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="27" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -2612,10 +2650,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="27" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -2641,10 +2677,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="27" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -2670,10 +2704,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="27" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -2699,10 +2731,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="27" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -2727,24 +2757,23 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="15" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  MANTENIMIENTO</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
+      <c r="B19" s="25" t="n"/>
+      <c r="C19" s="25" t="n"/>
+      <c r="D19" s="25" t="n"/>
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="25" t="n"/>
+      <c r="G19" s="26" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="27" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -2770,10 +2799,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="27" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -2799,10 +2826,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="27" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -2828,10 +2853,8 @@
       <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="27" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -2856,24 +2879,23 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="15" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  MARKETING Y ESTRATEGIA</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
+      <c r="B25" s="25" t="n"/>
+      <c r="C25" s="25" t="n"/>
+      <c r="D25" s="25" t="n"/>
+      <c r="E25" s="25" t="n"/>
+      <c r="F25" s="25" t="n"/>
+      <c r="G25" s="26" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="27" t="n">
+        <v>15</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -2899,10 +2921,8 @@
       <c r="G26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="27" t="n">
+        <v>16</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
@@ -2928,10 +2948,8 @@
       <c r="G27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="27" t="n">
+        <v>17</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
@@ -2957,10 +2975,8 @@
       <c r="G28" s="15" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A29" s="27" t="n">
+        <v>18</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -2985,6 +3001,8 @@
       <c r="F29" s="14" t="n"/>
       <c r="G29" s="15" t="n"/>
     </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
@@ -2993,17 +3011,19 @@
       </c>
       <c r="D32" s="19">
         <f>COUNTIF(F5:F30,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F32" s="19" t="n">
-        <v>18</v>
-      </c>
-    </row>
+      <c r="F32" s="19">
+        <f>COUNTIF(B5:B30,"?*")</f>
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
@@ -3011,13 +3031,17 @@
         </is>
       </c>
       <c r="B34" s="15" t="n"/>
+      <c r="C34" s="25" t="n"/>
+      <c r="D34" s="26" t="n"/>
       <c r="E34" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F34" s="15" t="n"/>
-    </row>
+      <c r="G34" s="26" t="n"/>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="21" t="inlineStr">
         <is>
@@ -3029,21 +3053,34 @@
   <mergeCells count="9">
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G30">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3052,18 +3089,18 @@
   <sheetPr>
     <tabColor rgb="009C27B0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3080,10 +3117,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3108,7 +3146,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -3123,18 +3161,16 @@
           <t xml:space="preserve">  TRASPASO DE INFORMACIÓN</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n"/>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n"/>
-      <c r="E5" s="23" t="n"/>
-      <c r="F5" s="23" t="n"/>
-      <c r="G5" s="23" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="27" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -3160,10 +3196,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="27" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -3189,10 +3223,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="27" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -3218,10 +3250,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="27" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -3247,10 +3277,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -3275,24 +3303,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  ESTADO DEL LOCAL</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n"/>
-      <c r="C12" s="23" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="23" t="n"/>
-      <c r="F12" s="23" t="n"/>
-      <c r="G12" s="23" t="n"/>
+      <c r="B12" s="25" t="n"/>
+      <c r="C12" s="25" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="25" t="n"/>
+      <c r="F12" s="25" t="n"/>
+      <c r="G12" s="26" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="27" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -3318,10 +3345,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="27" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -3347,10 +3372,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="27" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -3376,10 +3399,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="27" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -3404,24 +3425,23 @@
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="15" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  CONFIRMACIÓN TURNO ENTRANTE</t>
         </is>
       </c>
-      <c r="B18" s="23" t="n"/>
-      <c r="C18" s="23" t="n"/>
-      <c r="D18" s="23" t="n"/>
-      <c r="E18" s="23" t="n"/>
-      <c r="F18" s="23" t="n"/>
-      <c r="G18" s="23" t="n"/>
+      <c r="B18" s="25" t="n"/>
+      <c r="C18" s="25" t="n"/>
+      <c r="D18" s="25" t="n"/>
+      <c r="E18" s="25" t="n"/>
+      <c r="F18" s="25" t="n"/>
+      <c r="G18" s="26" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="27" t="n">
+        <v>10</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -3447,10 +3467,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="27" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -3476,10 +3494,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="27" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -3504,6 +3520,8 @@
       <c r="F21" s="14" t="n"/>
       <c r="G21" s="15" t="n"/>
     </row>
+    <row r="22"/>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
@@ -3512,17 +3530,19 @@
       </c>
       <c r="D24" s="19">
         <f>COUNTIF(F5:F22,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F24" s="19" t="n">
-        <v>12</v>
-      </c>
-    </row>
+      <c r="F24" s="19">
+        <f>COUNTIF(B5:B22,"?*")</f>
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
@@ -3530,13 +3550,17 @@
         </is>
       </c>
       <c r="B26" s="15" t="n"/>
+      <c r="C26" s="25" t="n"/>
+      <c r="D26" s="26" t="n"/>
       <c r="E26" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F26" s="15" t="n"/>
-    </row>
+      <c r="G26" s="26" t="n"/>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="21" t="inlineStr">
         <is>
@@ -3555,12 +3579,25 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="F26:G26"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G22">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F19 F20 F21" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="portrait"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas/03-tareas-manager.xlsx
@@ -14,14 +14,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Handover Turno" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$45</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Diario Manager'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Diario Manager'!$A$1:$G$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Diario Manager'!$A$1:$G$49</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Semanal Manager'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Semanal Manager'!$A$1:$G$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Semanal Manager'!$A$1:$G$51</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mensual Manager'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Mensual Manager'!$A$1:$G$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Mensual Manager'!$A$1:$G$41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Handover Turno'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Handover Turno'!$A$1:$G$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Handover Turno'!$A$1:$G$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -102,8 +103,22 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -138,6 +153,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F5F5F5"/>
         <bgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -211,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -259,6 +279,67 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -636,79 +717,222 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>Tareas del Manager / Gerente — Restaurante Casual</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Cómo usar estas plantillas</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+    <row r="6" ht="16" customHeight="1">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>▸ Checklist diario: imprime uno por día laborable</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="3" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>▸ Checklist semanal: imprime uno por semana</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="3" t="inlineStr">
+    <row r="8" ht="16" customHeight="1">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>▸ Checklist mensual: imprime uno por mes</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="3" t="inlineStr">
+    <row r="9" ht="16" customHeight="1">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>▸ Handover: imprime para cada cambio de turno</t>
         </is>
       </c>
     </row>
     <row r="10"/>
-    <row r="11">
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes · AI Chef Pro · aichef.pro</t>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>La semana va por DÍAS 1-5, no por lunes-viernes</t>
         </is>
       </c>
     </row>
     <row r="12"/>
-    <row r="13">
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>▸ Los bloques de «Semanal Manager» están numerados por orden de la semana, no por día del calendario: muchos restaurantes cierran el lunes y ese bloque se quedaba huérfano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>▸ La columna «Día» viene con Día 1…Día 5 (el orden de TU semana, no el del calendario): escribe encima el día real de tu local, es una celda verde. El bloque «FIN DE SEMANA» es el de sábado y domingo, que es cuando se factura la mitad de la semana.</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
+      <c r="B15" s="2" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="B27" s="29" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="29" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día (accesos, luces, clima, terraza).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="B35" s="30" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina, sala, barra).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="B36" s="30" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="B37" s="30" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. No se duplican: cada uno cubre un nivel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="B38" s="30" t="inlineStr">
+        <is>
+          <t>▸ Estás en 03-tareas-manager.xlsx: es una capa MÁS, no una repetición — el marco del día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="29" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="35" customHeight="1">
+      <c r="B42" s="29" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="29" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="B45" s="29" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -733,7 +957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -783,7 +1007,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -798,790 +1022,894 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  PRIMERA HORA (llegada)</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="26" t="n"/>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Revisar email y mensajes pendientes</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="39" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="n">
+      <c r="A7" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Revisar reservas del día y asignar mesas</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="39" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Verificar plantilla del día: ¿alguien ha faltado?</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="39" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="n">
+      <c r="A9" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Revisar incidencias del turno anterior</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D9" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="38" t="n"/>
+      <c r="G9" s="39" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="n">
+      <c r="A10" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Comprobar entregas de proveedores programadas</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="39" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="n"/>
+      <c r="B11" s="40" t="n"/>
+      <c r="C11" s="40" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
+      <c r="G11" s="40" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  PRE-SERVICIO</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="25" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="26" t="n"/>
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="33" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="n">
+      <c r="A13" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>Recorrido de inspección: cocina, sala, baños, terraza</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D13" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="39" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Verificar limpieza general del local</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D14" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="39" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Hablar con jefe de cocina: platos del día, incidencias</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D15" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>11:15</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="39" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>Revisar redes sociales: comentarios, reseñas nuevas</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D16" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E16" s="37" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="F16" s="38" t="n"/>
+      <c r="G16" s="39" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>Briefing pre-servicio con equipo de sala</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D17" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>11:45</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>Revisar redes sociales: comentarios, reseñas nuevas</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
-    </row>
-    <row r="18"/>
+      <c r="F17" s="38" t="n"/>
+      <c r="G17" s="39" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="40" t="n"/>
+      <c r="B18" s="40" t="n"/>
+      <c r="C18" s="40" t="n"/>
+      <c r="D18" s="40" t="n"/>
+      <c r="E18" s="40" t="n"/>
+      <c r="F18" s="40" t="n"/>
+      <c r="G18" s="40" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  DURANTE SERVICIO</t>
         </is>
       </c>
-      <c r="B19" s="25" t="n"/>
-      <c r="C19" s="25" t="n"/>
-      <c r="D19" s="25" t="n"/>
-      <c r="E19" s="25" t="n"/>
-      <c r="F19" s="25" t="n"/>
-      <c r="G19" s="26" t="n"/>
+      <c r="B19" s="32" t="n"/>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="32" t="n"/>
+      <c r="E19" s="32" t="n"/>
+      <c r="F19" s="32" t="n"/>
+      <c r="G19" s="33" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="n">
+      <c r="A20" s="34" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>Estar presente en sala durante picos de servicio</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="36" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="D20" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E20" s="37" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="F20" s="38" t="n"/>
+      <c r="G20" s="39" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="n">
+      <c r="A21" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>Saludar a clientes habituales / VIPs</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="36" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="D21" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E21" s="37" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="39" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="n">
+      <c r="A22" s="34" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>Gestionar reclamaciones o incidencias en sala</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="36" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="D22" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E22" s="37" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15" t="n"/>
+      <c r="F22" s="38" t="n"/>
+      <c r="G22" s="39" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="n">
+      <c r="A23" s="34" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>Supervisar tiempos de servicio</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="36" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="D23" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E23" s="37" t="inlineStr">
         <is>
           <t>Servicio</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15" t="n"/>
-    </row>
-    <row r="24"/>
+      <c r="F23" s="38" t="n"/>
+      <c r="G23" s="39" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="40" t="n"/>
+      <c r="B24" s="40" t="n"/>
+      <c r="C24" s="40" t="n"/>
+      <c r="D24" s="40" t="n"/>
+      <c r="E24" s="40" t="n"/>
+      <c r="F24" s="40" t="n"/>
+      <c r="G24" s="40" t="n"/>
+    </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  POST-SERVICIO</t>
         </is>
       </c>
-      <c r="B25" s="25" t="n"/>
-      <c r="C25" s="25" t="n"/>
-      <c r="D25" s="25" t="n"/>
-      <c r="E25" s="25" t="n"/>
-      <c r="F25" s="25" t="n"/>
-      <c r="G25" s="26" t="n"/>
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="32" t="n"/>
+      <c r="E25" s="32" t="n"/>
+      <c r="F25" s="32" t="n"/>
+      <c r="G25" s="33" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="n">
+      <c r="A26" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>Revisar comentarios del servicio con jefe cocina</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="C26" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D26" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E26" s="37" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="F26" s="38" t="n"/>
+      <c r="G26" s="39" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="n">
+      <c r="A27" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>Revisar ventas del mediodía en TPV</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="C27" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D27" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E27" s="37" t="inlineStr">
         <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="15" t="n"/>
+      <c r="F27" s="38" t="n"/>
+      <c r="G27" s="39" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="n">
+      <c r="A28" s="34" t="n">
         <v>17</v>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="35" t="inlineStr">
         <is>
           <t>Gestionar pedidos a proveedores para mañana</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="C28" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D28" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E28" s="37" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="15" t="n"/>
+      <c r="F28" s="38" t="n"/>
+      <c r="G28" s="39" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="27" t="n">
+      <c r="A29" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>Responder reseñas de Google / TripAdvisor</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="C29" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D29" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E29" s="37" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="15" t="n"/>
+      <c r="F29" s="38" t="n"/>
+      <c r="G29" s="39" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="n">
+      <c r="A30" s="34" t="n">
         <v>19</v>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>Actualizar redes sociales si aplica</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="C30" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D30" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E30" s="37" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="15" t="n"/>
-    </row>
-    <row r="31"/>
+      <c r="F30" s="38" t="n"/>
+      <c r="G30" s="39" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="40" t="n"/>
+      <c r="B31" s="40" t="n"/>
+      <c r="C31" s="40" t="n"/>
+      <c r="D31" s="40" t="n"/>
+      <c r="E31" s="40" t="n"/>
+      <c r="F31" s="40" t="n"/>
+      <c r="G31" s="40" t="n"/>
+    </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  CIERRE DEL DÍA</t>
         </is>
       </c>
-      <c r="B32" s="25" t="n"/>
-      <c r="C32" s="25" t="n"/>
-      <c r="D32" s="25" t="n"/>
-      <c r="E32" s="25" t="n"/>
-      <c r="F32" s="25" t="n"/>
-      <c r="G32" s="26" t="n"/>
+      <c r="B32" s="32" t="n"/>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="32" t="n"/>
+      <c r="E32" s="32" t="n"/>
+      <c r="F32" s="32" t="n"/>
+      <c r="G32" s="33" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="27" t="n">
+      <c r="A33" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>Cuadrar caja del día</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="C33" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D33" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E33" s="37" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="15" t="n"/>
+      <c r="F33" s="38" t="n"/>
+      <c r="G33" s="39" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="27" t="n">
+      <c r="A34" s="34" t="n">
         <v>21</v>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="35" t="inlineStr">
         <is>
           <t>Registrar ventas totales</t>
         </is>
       </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="C34" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D34" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E34" s="37" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F34" s="14" t="n"/>
-      <c r="G34" s="15" t="n"/>
+      <c r="F34" s="38" t="n"/>
+      <c r="G34" s="39" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="27" t="n">
+      <c r="A35" s="34" t="n">
         <v>22</v>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr">
+        <is>
+          <t>Cerrar y validar el registro diario de jornada del equipo (entradas, salidas y pausas)</t>
+        </is>
+      </c>
+      <c r="C35" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D35" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E35" s="37" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="F35" s="38" t="n"/>
+      <c r="G35" s="39" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="34" t="n">
+        <v>23</v>
+      </c>
+      <c r="B36" s="35" t="inlineStr">
         <is>
           <t>Anotar incidencias relevantes del día</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
+      <c r="C36" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D36" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E36" s="37" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F35" s="14" t="n"/>
-      <c r="G35" s="15" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="27" t="n">
-        <v>23</v>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="F36" s="38" t="n"/>
+      <c r="G36" s="39" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="34" t="n">
+        <v>24</v>
+      </c>
+      <c r="B37" s="35" t="inlineStr">
         <is>
           <t>Preparar notas para el turno de mañana</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="C37" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D37" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E37" s="37" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F36" s="14" t="n"/>
-      <c r="G36" s="15" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="27" t="n">
-        <v>24</v>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="F37" s="38" t="n"/>
+      <c r="G37" s="39" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="34" t="n">
+        <v>25</v>
+      </c>
+      <c r="B38" s="35" t="inlineStr">
         <is>
           <t>Verificar cierre completo del local</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="C38" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D38" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E38" s="37" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F37" s="14" t="n"/>
-      <c r="G37" s="15" t="n"/>
-    </row>
-    <row r="38"/>
-    <row r="39"/>
+      <c r="F38" s="38" t="n"/>
+      <c r="G38" s="39" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="42" t="n"/>
+      <c r="B39" s="43" t="n"/>
+      <c r="C39" s="36" t="n"/>
+      <c r="D39" s="37" t="n"/>
+      <c r="E39" s="37" t="n"/>
+      <c r="F39" s="38" t="n"/>
+      <c r="G39" s="39" t="n"/>
+    </row>
     <row r="40">
-      <c r="A40" s="19" t="inlineStr">
+      <c r="A40" s="42" t="n"/>
+      <c r="B40" s="43" t="n"/>
+      <c r="C40" s="36" t="n"/>
+      <c r="D40" s="37" t="n"/>
+      <c r="E40" s="37" t="n"/>
+      <c r="F40" s="38" t="n"/>
+      <c r="G40" s="39" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="42" t="n"/>
+      <c r="B41" s="43" t="n"/>
+      <c r="C41" s="36" t="n"/>
+      <c r="D41" s="37" t="n"/>
+      <c r="E41" s="37" t="n"/>
+      <c r="F41" s="38" t="n"/>
+      <c r="G41" s="39" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="42" t="n"/>
+      <c r="B42" s="43" t="n"/>
+      <c r="C42" s="36" t="n"/>
+      <c r="D42" s="37" t="n"/>
+      <c r="E42" s="37" t="n"/>
+      <c r="F42" s="38" t="n"/>
+      <c r="G42" s="39" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="42" t="n"/>
+      <c r="B43" s="43" t="n"/>
+      <c r="C43" s="36" t="n"/>
+      <c r="D43" s="37" t="n"/>
+      <c r="E43" s="37" t="n"/>
+      <c r="F43" s="38" t="n"/>
+      <c r="G43" s="39" t="n"/>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D40" s="19">
-        <f>COUNTIF(F5:F38,"✓")</f>
+      <c r="D45" s="19">
+        <f>COUNTIFS(B5:B43,"?*",F5:F43,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E40" s="20" t="inlineStr">
+      <c r="E45" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F40" s="19">
-        <f>COUNTIF(B5:B38,"?*")</f>
-        <v>24.0</v>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" s="19" t="inlineStr">
+      <c r="F45" s="19">
+        <f>COUNTIF(B5:B43,"?*")-COUNTIF(F5:F43,"N/A")</f>
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B42" s="15" t="n"/>
-      <c r="C42" s="25" t="n"/>
-      <c r="D42" s="26" t="n"/>
-      <c r="E42" s="19" t="inlineStr">
+      <c r="B47" s="44" t="n"/>
+      <c r="C47" s="25" t="n"/>
+      <c r="D47" s="26" t="n"/>
+      <c r="E47" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F42" s="15" t="n"/>
-      <c r="G42" s="26" t="n"/>
-    </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" s="21" t="inlineStr">
+      <c r="F47" s="44" t="n"/>
+      <c r="G47" s="26" t="n"/>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="10">
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="F47:G47"/>
     <mergeCell ref="A32:G32"/>
-    <mergeCell ref="B42:D42"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="B47:D47"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A45:C45"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="F42:G42"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G38">
+  <conditionalFormatting sqref="A5:G43">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30 F33 F34 F35 F36 F37 F38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1605,7 +1933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1627,7 +1955,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable turno: _________________________</t>
+          <t>Semana del ___/___/______ al ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1983,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Día</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1670,709 +1998,917 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  LUNES — PLANIFICACIÓN</t>
-        </is>
-      </c>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="26" t="n"/>
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DÍA 1 — PLANIFICACIÓN</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Revisar ventas de la semana anterior</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="37" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="39" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="n">
+      <c r="A7" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Analizar platos más y menos vendidos</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="37" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="39" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Planificar carta/menú de la semana</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="37" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="39" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="n">
+      <c r="A9" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Revisar y confirmar turnos de la semana</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D9" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="37" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F9" s="38" t="n"/>
+      <c r="G9" s="39" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="n">
+      <c r="A10" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Reunión semanal con jefe de cocina</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="37" t="inlineStr">
+        <is>
+          <t>Día 1</t>
+        </is>
+      </c>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="39" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="n"/>
+      <c r="B11" s="40" t="n"/>
+      <c r="C11" s="40" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
+      <c r="G11" s="40" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  MARTES — PROVEEDORES</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="25" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="26" t="n"/>
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DÍA 2 — PROVEEDORES</t>
+        </is>
+      </c>
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="33" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="n">
+      <c r="A13" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>Comparar precios de proveedores principales</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="C13" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D13" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="inlineStr">
+        <is>
+          <t>Día 2</t>
+        </is>
+      </c>
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="39" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Gestionar pedidos semanales</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="C14" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D14" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E14" s="37" t="inlineStr">
+        <is>
+          <t>Día 2</t>
+        </is>
+      </c>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="39" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Negociar condiciones si hay subidas de precio</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="C15" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D15" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="37" t="inlineStr">
+        <is>
+          <t>Día 2</t>
+        </is>
+      </c>
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="39" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Revisar albaranes pendientes de factura</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
-    </row>
-    <row r="17"/>
+      <c r="C16" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D16" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E16" s="37" t="inlineStr">
+        <is>
+          <t>Día 2</t>
+        </is>
+      </c>
+      <c r="F16" s="38" t="n"/>
+      <c r="G16" s="39" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="n"/>
+      <c r="B17" s="40" t="n"/>
+      <c r="C17" s="40" t="n"/>
+      <c r="D17" s="40" t="n"/>
+      <c r="E17" s="40" t="n"/>
+      <c r="F17" s="40" t="n"/>
+      <c r="G17" s="40" t="n"/>
+    </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  MIÉRCOLES — EQUIPO</t>
-        </is>
-      </c>
-      <c r="B18" s="25" t="n"/>
-      <c r="C18" s="25" t="n"/>
-      <c r="D18" s="25" t="n"/>
-      <c r="E18" s="25" t="n"/>
-      <c r="F18" s="25" t="n"/>
-      <c r="G18" s="26" t="n"/>
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DÍA 3 — EQUIPO</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="n"/>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="32" t="n"/>
+      <c r="E18" s="32" t="n"/>
+      <c r="F18" s="32" t="n"/>
+      <c r="G18" s="33" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="n">
+      <c r="A19" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>Reunión breve con equipo de sala</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="C19" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D19" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E19" s="37" t="inlineStr">
+        <is>
+          <t>Día 3</t>
+        </is>
+      </c>
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="39" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="n">
+      <c r="A20" s="34" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>Evaluar rendimiento individual (informal)</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="C20" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D20" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E20" s="37" t="inlineStr">
+        <is>
+          <t>Día 3</t>
+        </is>
+      </c>
+      <c r="F20" s="38" t="n"/>
+      <c r="G20" s="39" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="n">
+      <c r="A21" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>Gestionar solicitudes de vacaciones/cambios</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="C21" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D21" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E21" s="37" t="inlineStr">
+        <is>
+          <t>Día 3</t>
+        </is>
+      </c>
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="39" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="n">
+      <c r="A22" s="34" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>Revisar uniformes y presentación del equipo</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15" t="n"/>
-    </row>
-    <row r="23"/>
+      <c r="C22" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D22" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E22" s="37" t="inlineStr">
+        <is>
+          <t>Día 3</t>
+        </is>
+      </c>
+      <c r="F22" s="38" t="n"/>
+      <c r="G22" s="39" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="40" t="n"/>
+      <c r="B23" s="40" t="n"/>
+      <c r="C23" s="40" t="n"/>
+      <c r="D23" s="40" t="n"/>
+      <c r="E23" s="40" t="n"/>
+      <c r="F23" s="40" t="n"/>
+      <c r="G23" s="40" t="n"/>
+    </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  JUEVES — CALIDAD</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="n"/>
-      <c r="C24" s="25" t="n"/>
-      <c r="D24" s="25" t="n"/>
-      <c r="E24" s="25" t="n"/>
-      <c r="F24" s="25" t="n"/>
-      <c r="G24" s="26" t="n"/>
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DÍA 4 — CALIDAD</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="n"/>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="32" t="n"/>
+      <c r="E24" s="32" t="n"/>
+      <c r="F24" s="32" t="n"/>
+      <c r="G24" s="33" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="n">
+      <c r="A25" s="34" t="n">
         <v>14</v>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>Inspección de cámaras: orden, limpieza, FIFO</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="C25" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D25" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E25" s="37" t="inlineStr">
+        <is>
+          <t>Día 4</t>
+        </is>
+      </c>
+      <c r="F25" s="38" t="n"/>
+      <c r="G25" s="39" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="n">
+      <c r="A26" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>Revisión de registros APPCC de la semana</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="B26" s="35" t="inlineStr">
+        <is>
+          <t>Revisar los registros de higiene de la semana: si tienes el Pack APPCC, en sus hojas; si no, en las tuyas</t>
+        </is>
+      </c>
+      <c r="C26" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D26" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E26" s="37" t="inlineStr">
+        <is>
+          <t>Día 4</t>
+        </is>
+      </c>
+      <c r="F26" s="38" t="n"/>
+      <c r="G26" s="39" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="n">
+      <c r="A27" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>Verificar stock de productos de limpieza</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="15" t="n"/>
+      <c r="C27" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D27" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E27" s="37" t="inlineStr">
+        <is>
+          <t>Día 4</t>
+        </is>
+      </c>
+      <c r="F27" s="38" t="n"/>
+      <c r="G27" s="39" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="n">
+      <c r="A28" s="34" t="n">
         <v>17</v>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="35" t="inlineStr">
         <is>
           <t>Probar 2-3 platos de la carta (control calidad)</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="15" t="n"/>
-    </row>
-    <row r="29"/>
+      <c r="C28" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D28" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E28" s="37" t="inlineStr">
+        <is>
+          <t>Día 4</t>
+        </is>
+      </c>
+      <c r="F28" s="38" t="n"/>
+      <c r="G28" s="39" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="40" t="n"/>
+      <c r="B29" s="40" t="n"/>
+      <c r="C29" s="40" t="n"/>
+      <c r="D29" s="40" t="n"/>
+      <c r="E29" s="40" t="n"/>
+      <c r="F29" s="40" t="n"/>
+      <c r="G29" s="40" t="n"/>
+    </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  VIERNES — MARKETING Y ADMIN</t>
-        </is>
-      </c>
-      <c r="B30" s="25" t="n"/>
-      <c r="C30" s="25" t="n"/>
-      <c r="D30" s="25" t="n"/>
-      <c r="E30" s="25" t="n"/>
-      <c r="F30" s="25" t="n"/>
-      <c r="G30" s="26" t="n"/>
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DÍA 5 — MARKETING Y ADMIN</t>
+        </is>
+      </c>
+      <c r="B30" s="32" t="n"/>
+      <c r="C30" s="32" t="n"/>
+      <c r="D30" s="32" t="n"/>
+      <c r="E30" s="32" t="n"/>
+      <c r="F30" s="32" t="n"/>
+      <c r="G30" s="33" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="27" t="n">
+      <c r="A31" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>Planificar publicaciones de redes sociales del fin de semana</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="15" t="n"/>
+      <c r="C31" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D31" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E31" s="37" t="inlineStr">
+        <is>
+          <t>Día 5</t>
+        </is>
+      </c>
+      <c r="F31" s="38" t="n"/>
+      <c r="G31" s="39" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="27" t="n">
+      <c r="A32" s="34" t="n">
         <v>19</v>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="35" t="inlineStr">
         <is>
           <t>Revisar reservas del fin de semana</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="15" t="n"/>
+      <c r="C32" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D32" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E32" s="37" t="inlineStr">
+        <is>
+          <t>Día 5</t>
+        </is>
+      </c>
+      <c r="F32" s="38" t="n"/>
+      <c r="G32" s="39" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="27" t="n">
+      <c r="A33" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>Verificar stock suficiente para fin de semana</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="15" t="n"/>
+      <c r="C33" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D33" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E33" s="37" t="inlineStr">
+        <is>
+          <t>Día 5</t>
+        </is>
+      </c>
+      <c r="F33" s="38" t="n"/>
+      <c r="G33" s="39" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="27" t="n">
+      <c r="A34" s="34" t="n">
         <v>21</v>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="35" t="inlineStr">
         <is>
           <t>Cerrar semana administrativa: facturas, pagos</t>
         </is>
       </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="n"/>
-      <c r="G34" s="15" t="n"/>
-    </row>
-    <row r="35"/>
-    <row r="36"/>
+      <c r="C34" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D34" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E34" s="37" t="inlineStr">
+        <is>
+          <t>Día 5</t>
+        </is>
+      </c>
+      <c r="F34" s="38" t="n"/>
+      <c r="G34" s="39" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="42" t="n"/>
+      <c r="B35" s="43" t="n"/>
+      <c r="C35" s="36" t="n"/>
+      <c r="D35" s="37" t="n"/>
+      <c r="E35" s="37" t="n"/>
+      <c r="F35" s="38" t="n"/>
+      <c r="G35" s="39" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FIN DE SEMANA</t>
+        </is>
+      </c>
+      <c r="B36" s="32" t="n"/>
+      <c r="C36" s="32" t="n"/>
+      <c r="D36" s="32" t="n"/>
+      <c r="E36" s="32" t="n"/>
+      <c r="F36" s="32" t="n"/>
+      <c r="G36" s="33" t="n"/>
+    </row>
     <row r="37">
-      <c r="A37" s="19" t="inlineStr">
+      <c r="A37" s="34" t="n">
+        <v>22</v>
+      </c>
+      <c r="B37" s="35" t="inlineStr">
+        <is>
+          <t>Control de tiempos de espera en los picos de mediodía y de noche</t>
+        </is>
+      </c>
+      <c r="C37" s="36" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="D37" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E37" s="37" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="F37" s="38" t="n"/>
+      <c r="G37" s="39" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="34" t="n">
+        <v>23</v>
+      </c>
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>Reposición entre servicios: barra, bodega y mise en place de la noche</t>
+        </is>
+      </c>
+      <c r="C38" s="36" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D38" s="37" t="inlineStr">
+        <is>
+          <t>Encargado</t>
+        </is>
+      </c>
+      <c r="E38" s="37" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="F38" s="38" t="n"/>
+      <c r="G38" s="39" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="34" t="n">
+        <v>24</v>
+      </c>
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>Cerrar las reservas del domingo y confirmar por teléfono los grupos</t>
+        </is>
+      </c>
+      <c r="C39" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D39" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E39" s="37" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="F39" s="38" t="n"/>
+      <c r="G39" s="39" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="34" t="n">
+        <v>25</v>
+      </c>
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>Recuento del producto crítico para el lunes y pedido de urgencia si falta</t>
+        </is>
+      </c>
+      <c r="C40" s="36" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D40" s="37" t="inlineStr">
+        <is>
+          <t>Sous Chef</t>
+        </is>
+      </c>
+      <c r="E40" s="37" t="inlineStr">
+        <is>
+          <t>Domingo</t>
+        </is>
+      </c>
+      <c r="F40" s="38" t="n"/>
+      <c r="G40" s="39" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="42" t="n"/>
+      <c r="B41" s="43" t="n"/>
+      <c r="C41" s="36" t="n"/>
+      <c r="D41" s="37" t="n"/>
+      <c r="E41" s="37" t="n"/>
+      <c r="F41" s="38" t="n"/>
+      <c r="G41" s="39" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="42" t="n"/>
+      <c r="B42" s="43" t="n"/>
+      <c r="C42" s="36" t="n"/>
+      <c r="D42" s="37" t="n"/>
+      <c r="E42" s="37" t="n"/>
+      <c r="F42" s="38" t="n"/>
+      <c r="G42" s="39" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="42" t="n"/>
+      <c r="B43" s="43" t="n"/>
+      <c r="C43" s="36" t="n"/>
+      <c r="D43" s="37" t="n"/>
+      <c r="E43" s="37" t="n"/>
+      <c r="F43" s="38" t="n"/>
+      <c r="G43" s="39" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="42" t="n"/>
+      <c r="B44" s="43" t="n"/>
+      <c r="C44" s="36" t="n"/>
+      <c r="D44" s="37" t="n"/>
+      <c r="E44" s="37" t="n"/>
+      <c r="F44" s="38" t="n"/>
+      <c r="G44" s="39" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="42" t="n"/>
+      <c r="B45" s="43" t="n"/>
+      <c r="C45" s="36" t="n"/>
+      <c r="D45" s="37" t="n"/>
+      <c r="E45" s="37" t="n"/>
+      <c r="F45" s="38" t="n"/>
+      <c r="G45" s="39" t="n"/>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D37" s="19">
-        <f>COUNTIF(F5:F35,"✓")</f>
+      <c r="D47" s="19">
+        <f>COUNTIFS(B5:B45,"?*",F5:F45,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E37" s="20" t="inlineStr">
+      <c r="E47" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F37" s="19">
-        <f>COUNTIF(B5:B35,"?*")</f>
-        <v>21.0</v>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="19" t="inlineStr">
+      <c r="F47" s="19">
+        <f>COUNTIF(B5:B45,"?*")-COUNTIF(F5:F45,"N/A")</f>
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B39" s="15" t="n"/>
-      <c r="C39" s="25" t="n"/>
-      <c r="D39" s="26" t="n"/>
-      <c r="E39" s="19" t="inlineStr">
+      <c r="B49" s="44" t="n"/>
+      <c r="C49" s="25" t="n"/>
+      <c r="D49" s="26" t="n"/>
+      <c r="E49" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F39" s="15" t="n"/>
-      <c r="G39" s="26" t="n"/>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" s="21" t="inlineStr">
+      <c r="F49" s="44" t="n"/>
+      <c r="G49" s="26" t="n"/>
+    </row>
+    <row r="50"/>
+    <row r="51">
+      <c r="A51" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="11">
     <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A36:G36"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="F49:G49"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="B49:D49"/>
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="A47:C47"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G35">
+  <conditionalFormatting sqref="A5:G45">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F19 F20 F21 F22 F25 F26 F27 F28 F31 F32 F33 F34 F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F19 F20 F21 F22 F25 F26 F27 F28 F31 F32 F33 F34 F37 F38 F39 F40 F41 F42 F43 F44 F45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2396,7 +2932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2418,7 +2954,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable turno: _________________________</t>
+          <t>Mes: ________________   Año: ______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2982,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cadencia</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -2461,613 +2997,709 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  FINANZAS</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="26" t="n"/>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Revisar P&amp;L del mes (ingresos vs gastos)</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>Día 1-3</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="39" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="n">
+      <c r="A7" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Calcular food cost real vs objetivo</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>Día 1-3</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="39" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Calcular labor cost real vs objetivo</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>Día 1-3</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="39" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="n">
+      <c r="A9" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Revisar facturas pendientes de proveedores</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D9" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>Día 1-3</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="38" t="n"/>
+      <c r="G9" s="39" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="n">
+      <c r="A10" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Analizar ticket medio y evolución</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>Día 1-3</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="39" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="n"/>
+      <c r="B11" s="40" t="n"/>
+      <c r="C11" s="40" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
+      <c r="G11" s="40" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  EQUIPO</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="25" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="26" t="n"/>
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="33" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="n">
+      <c r="A13" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>Evaluación formal de rendimiento del equipo</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D13" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="39" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Detectar necesidades de formación</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D14" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="39" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Revisar cumplimiento de horarios del mes</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D15" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="39" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>Archivar los registros de jornada del mes (hay que conservarlos 4 años)</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D16" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E16" s="37" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="F16" s="38" t="n"/>
+      <c r="G16" s="39" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>Planificar turnos del mes siguiente</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D17" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="F17" s="38" t="n"/>
+      <c r="G17" s="39" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>Gestionar nóminas y variables</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="C18" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D18" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E18" s="37" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
-    </row>
-    <row r="18"/>
+      <c r="F18" s="38" t="n"/>
+      <c r="G18" s="39" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="40" t="n"/>
+      <c r="B19" s="40" t="n"/>
+      <c r="C19" s="40" t="n"/>
+      <c r="D19" s="40" t="n"/>
+      <c r="E19" s="40" t="n"/>
+      <c r="F19" s="40" t="n"/>
+      <c r="G19" s="40" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  MANTENIMIENTO</t>
         </is>
       </c>
-      <c r="B19" s="25" t="n"/>
-      <c r="C19" s="25" t="n"/>
-      <c r="D19" s="25" t="n"/>
-      <c r="E19" s="25" t="n"/>
-      <c r="F19" s="25" t="n"/>
-      <c r="G19" s="26" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="27" t="n">
-        <v>11</v>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="32" t="n"/>
+      <c r="C20" s="32" t="n"/>
+      <c r="D20" s="32" t="n"/>
+      <c r="E20" s="32" t="n"/>
+      <c r="F20" s="32" t="n"/>
+      <c r="G20" s="33" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>Revisión de equipos de cocina (estado general)</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="C21" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D21" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E21" s="37" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="27" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="39" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>Programar mantenimiento preventivo si necesario</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="C22" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D22" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E22" s="37" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="27" t="n">
-        <v>13</v>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="F22" s="38" t="n"/>
+      <c r="G22" s="39" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="34" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>Revisar extintores y salidas de emergencia</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="C23" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D23" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E23" s="37" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="27" t="n">
-        <v>14</v>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="F23" s="38" t="n"/>
+      <c r="G23" s="39" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="34" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>Verificar estado de mobiliario (mesas, sillas)</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="C24" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D24" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E24" s="37" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15" t="n"/>
-    </row>
-    <row r="24"/>
+      <c r="F24" s="38" t="n"/>
+      <c r="G24" s="39" t="n"/>
+    </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="40" t="n"/>
+      <c r="B25" s="40" t="n"/>
+      <c r="C25" s="40" t="n"/>
+      <c r="D25" s="40" t="n"/>
+      <c r="E25" s="40" t="n"/>
+      <c r="F25" s="40" t="n"/>
+      <c r="G25" s="40" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  MARKETING Y ESTRATEGIA</t>
         </is>
       </c>
-      <c r="B25" s="25" t="n"/>
-      <c r="C25" s="25" t="n"/>
-      <c r="D25" s="25" t="n"/>
-      <c r="E25" s="25" t="n"/>
-      <c r="F25" s="25" t="n"/>
-      <c r="G25" s="26" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="32" t="n"/>
+      <c r="C26" s="32" t="n"/>
+      <c r="D26" s="32" t="n"/>
+      <c r="E26" s="32" t="n"/>
+      <c r="F26" s="32" t="n"/>
+      <c r="G26" s="33" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="34" t="n">
+        <v>16</v>
+      </c>
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>Analizar reseñas del mes: tendencias y puntos débiles</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="C27" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D27" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E27" s="37" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="15" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="27" t="n">
-        <v>16</v>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="F27" s="38" t="n"/>
+      <c r="G27" s="39" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="34" t="n">
+        <v>17</v>
+      </c>
+      <c r="B28" s="35" t="inlineStr">
         <is>
           <t>Planificar promociones o eventos del mes siguiente</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="C28" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D28" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E28" s="37" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="15" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="27" t="n">
-        <v>17</v>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="F28" s="38" t="n"/>
+      <c r="G28" s="39" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="34" t="n">
+        <v>18</v>
+      </c>
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>Actualizar carta si hay cambios estacionales</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="C29" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D29" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E29" s="37" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="15" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="27" t="n">
-        <v>18</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="F29" s="38" t="n"/>
+      <c r="G29" s="39" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="34" t="n">
+        <v>19</v>
+      </c>
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>Revisar posicionamiento en Google Maps</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="C30" s="36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D30" s="37" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E30" s="37" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="15" t="n"/>
-    </row>
-    <row r="30"/>
-    <row r="31"/>
+      <c r="F30" s="38" t="n"/>
+      <c r="G30" s="39" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="42" t="n"/>
+      <c r="B31" s="43" t="n"/>
+      <c r="C31" s="36" t="n"/>
+      <c r="D31" s="37" t="n"/>
+      <c r="E31" s="37" t="n"/>
+      <c r="F31" s="38" t="n"/>
+      <c r="G31" s="39" t="n"/>
+    </row>
     <row r="32">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="A32" s="42" t="n"/>
+      <c r="B32" s="43" t="n"/>
+      <c r="C32" s="36" t="n"/>
+      <c r="D32" s="37" t="n"/>
+      <c r="E32" s="37" t="n"/>
+      <c r="F32" s="38" t="n"/>
+      <c r="G32" s="39" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="42" t="n"/>
+      <c r="B33" s="43" t="n"/>
+      <c r="C33" s="36" t="n"/>
+      <c r="D33" s="37" t="n"/>
+      <c r="E33" s="37" t="n"/>
+      <c r="F33" s="38" t="n"/>
+      <c r="G33" s="39" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="42" t="n"/>
+      <c r="B34" s="43" t="n"/>
+      <c r="C34" s="36" t="n"/>
+      <c r="D34" s="37" t="n"/>
+      <c r="E34" s="37" t="n"/>
+      <c r="F34" s="38" t="n"/>
+      <c r="G34" s="39" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="42" t="n"/>
+      <c r="B35" s="43" t="n"/>
+      <c r="C35" s="36" t="n"/>
+      <c r="D35" s="37" t="n"/>
+      <c r="E35" s="37" t="n"/>
+      <c r="F35" s="38" t="n"/>
+      <c r="G35" s="39" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D32" s="19">
-        <f>COUNTIF(F5:F30,"✓")</f>
+      <c r="D37" s="19">
+        <f>COUNTIFS(B5:B35,"?*",F5:F35,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E32" s="20" t="inlineStr">
+      <c r="E37" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F32" s="19">
-        <f>COUNTIF(B5:B30,"?*")</f>
-        <v>18.0</v>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="F37" s="19">
+        <f>COUNTIF(B5:B35,"?*")-COUNTIF(F5:F35,"N/A")</f>
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B34" s="15" t="n"/>
-      <c r="C34" s="25" t="n"/>
-      <c r="D34" s="26" t="n"/>
-      <c r="E34" s="19" t="inlineStr">
+      <c r="B39" s="44" t="n"/>
+      <c r="C39" s="25" t="n"/>
+      <c r="D39" s="26" t="n"/>
+      <c r="E39" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F34" s="15" t="n"/>
-      <c r="G34" s="26" t="n"/>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="21" t="inlineStr">
+      <c r="F39" s="44" t="n"/>
+      <c r="G39" s="26" t="n"/>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="9">
     <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A32:C32"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="F39:G39"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="B39:D39"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G30">
+  <conditionalFormatting sqref="A5:G35">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F21 F22 F23 F24 F27 F28 F29 F30 F31 F32 F33 F34 F35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3091,7 +3723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3141,7 +3773,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -3156,436 +3788,497 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">  TRASPASO DE INFORMACIÓN</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="26" t="n"/>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Incidencias del turno que sale</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>Encargado saliente</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="39" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="n">
+      <c r="A7" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Mesas ocupadas y estado de cada una</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>Encargado saliente</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="38" t="n"/>
+      <c r="G7" s="39" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Reservas pendientes del turno entrante</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Encargado saliente</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="F8" s="38" t="n"/>
+      <c r="G8" s="39" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="n">
+      <c r="A9" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Productos agotados (86s)</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>Encargado saliente</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="38" t="n"/>
+      <c r="G9" s="39" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="n">
+      <c r="A10" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Reclamaciones o clientes especiales</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="37" t="inlineStr">
         <is>
           <t>Encargado saliente</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-    </row>
-    <row r="11"/>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="39" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="n"/>
+      <c r="B11" s="40" t="n"/>
+      <c r="C11" s="40" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
+      <c r="G11" s="40" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">  ESTADO DEL LOCAL</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="25" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="26" t="n"/>
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="33" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="n">
+      <c r="A13" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>Estado de limpieza: cocina, sala, baños</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>Encargado saliente</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="39" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Estado de caja: fondo correcto</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="37" t="inlineStr">
         <is>
           <t>Encargado saliente</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="39" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Pedidos pendientes de recibir</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>Encargado saliente</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="39" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Tareas pendientes no completadas</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="37" t="inlineStr">
         <is>
           <t>Encargado saliente</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="37" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
-    </row>
-    <row r="17"/>
+      <c r="F16" s="38" t="n"/>
+      <c r="G16" s="39" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="n"/>
+      <c r="B17" s="40" t="n"/>
+      <c r="C17" s="40" t="n"/>
+      <c r="D17" s="40" t="n"/>
+      <c r="E17" s="40" t="n"/>
+      <c r="F17" s="40" t="n"/>
+      <c r="G17" s="40" t="n"/>
+    </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">  CONFIRMACIÓN TURNO ENTRANTE</t>
         </is>
       </c>
-      <c r="B18" s="25" t="n"/>
-      <c r="C18" s="25" t="n"/>
-      <c r="D18" s="25" t="n"/>
-      <c r="E18" s="25" t="n"/>
-      <c r="F18" s="25" t="n"/>
-      <c r="G18" s="26" t="n"/>
+      <c r="B18" s="32" t="n"/>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="32" t="n"/>
+      <c r="E18" s="32" t="n"/>
+      <c r="F18" s="32" t="n"/>
+      <c r="G18" s="33" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="n">
+      <c r="A19" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>Turno entrante confirma recepción de información</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="36" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="37" t="inlineStr">
         <is>
           <t>Encargado entrante</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="37" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="F19" s="38" t="n"/>
+      <c r="G19" s="39" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="n">
+      <c r="A20" s="34" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>Recorrido rápido de verificación</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="36" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="37" t="inlineStr">
         <is>
           <t>Encargado entrante</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="37" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="F20" s="38" t="n"/>
+      <c r="G20" s="39" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="n">
+      <c r="A21" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>Firma de traspaso: ambos encargados</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="36" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="37" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="37" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
-    </row>
-    <row r="22"/>
-    <row r="23"/>
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="39" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="n"/>
+      <c r="B22" s="43" t="n"/>
+      <c r="C22" s="36" t="n"/>
+      <c r="D22" s="37" t="n"/>
+      <c r="E22" s="37" t="n"/>
+      <c r="F22" s="38" t="n"/>
+      <c r="G22" s="39" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="n"/>
+      <c r="B23" s="43" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="37" t="n"/>
+      <c r="E23" s="37" t="n"/>
+      <c r="F23" s="38" t="n"/>
+      <c r="G23" s="39" t="n"/>
+    </row>
     <row r="24">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="D24" s="19">
-        <f>COUNTIF(F5:F22,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="F24" s="19">
-        <f>COUNTIF(B5:B22,"?*")</f>
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="25"/>
+      <c r="A24" s="42" t="n"/>
+      <c r="B24" s="43" t="n"/>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="37" t="n"/>
+      <c r="E24" s="37" t="n"/>
+      <c r="F24" s="38" t="n"/>
+      <c r="G24" s="39" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="42" t="n"/>
+      <c r="B25" s="43" t="n"/>
+      <c r="C25" s="36" t="n"/>
+      <c r="D25" s="37" t="n"/>
+      <c r="E25" s="37" t="n"/>
+      <c r="F25" s="38" t="n"/>
+      <c r="G25" s="39" t="n"/>
+    </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>Verificado por:</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="n"/>
-      <c r="C26" s="25" t="n"/>
-      <c r="D26" s="26" t="n"/>
-      <c r="E26" s="19" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="n"/>
-      <c r="G26" s="26" t="n"/>
+      <c r="A26" s="42" t="n"/>
+      <c r="B26" s="43" t="n"/>
+      <c r="C26" s="36" t="n"/>
+      <c r="D26" s="37" t="n"/>
+      <c r="E26" s="37" t="n"/>
+      <c r="F26" s="38" t="n"/>
+      <c r="G26" s="39" t="n"/>
     </row>
     <row r="27"/>
     <row r="28">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D28" s="19">
+        <f>COUNTIFS(B5:B26,"?*",F5:F26,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F28" s="19">
+        <f>COUNTIF(B5:B26,"?*")-COUNTIF(F5:F26,"N/A")</f>
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>Verificado por:</t>
+        </is>
+      </c>
+      <c r="B30" s="44" t="n"/>
+      <c r="C30" s="25" t="n"/>
+      <c r="D30" s="26" t="n"/>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>Firma:</t>
+        </is>
+      </c>
+      <c r="F30" s="44" t="n"/>
+      <c r="G30" s="26" t="n"/>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Restaurante Casual · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="A28:C28"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G22">
+  <conditionalFormatting sqref="A5:G26">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F19 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/astro-site/public/dl/kit-tareas/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas/03-tareas-manager.xlsx
@@ -824,6 +824,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="29" t="inlineStr">
         <is>
@@ -831,6 +832,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="32" customHeight="1">
       <c r="B24" s="30" t="inlineStr">
         <is>
@@ -845,6 +847,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="29" t="inlineStr">
         <is>
@@ -852,6 +855,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29" ht="32" customHeight="1">
       <c r="B29" s="30" t="inlineStr">
         <is>
@@ -866,6 +870,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="29" t="inlineStr">
         <is>
@@ -873,10 +878,11 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="32" customHeight="1">
+    <row r="33"/>
+    <row r="34" ht="16" customHeight="1">
       <c r="B34" s="30" t="inlineStr">
         <is>
-          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día (accesos, luces, clima, terraza).</t>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
         </is>
       </c>
     </row>
@@ -894,10 +900,10 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="16" customHeight="1">
+    <row r="37" ht="48" customHeight="1">
       <c r="B37" s="30" t="inlineStr">
         <is>
-          <t>▸ Orden de uso: local → áreas → caja. No se duplican: cada uno cubre un nivel.</t>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
         </is>
       </c>
     </row>
@@ -908,6 +914,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="29" t="inlineStr">
         <is>
@@ -915,6 +922,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42" ht="35" customHeight="1">
       <c r="B42" s="29" t="inlineStr">
         <is>
@@ -929,6 +937,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="29" t="inlineStr">
         <is>
@@ -1909,7 +1918,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F26 F27 F28 F29 F30 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2908,7 +2917,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F19 F20 F21 F22 F25 F26 F27 F28 F31 F32 F33 F34 F37 F38 F39 F40 F41 F42 F43 F44 F45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F19 F20 F21 F22 F25 F26 F27 F28 F31 F32 F33 F34 F37 F38 F39 F40 F41 F42 F43 F44 F45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3699,7 +3708,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F21 F22 F23 F24 F27 F28 F29 F30 F31 F32 F33 F34 F35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F18 F21 F22 F23 F24 F27 F28 F29 F30 F31 F32 F33 F34 F35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4265,9 +4274,9 @@
   <mergeCells count="8">
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A28:C28"/>
@@ -4278,7 +4287,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F19 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓ (hecha), — (no hecha) o N/A (no aplica). Las marcadas N/A o — salen del total." type="list" errorStyle="stop">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F19 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
